--- a/excel_db/staff_users.xlsx
+++ b/excel_db/staff_users.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>username</t>
   </si>
@@ -31,13 +31,25 @@
     <t>boateng</t>
   </si>
   <si>
+    <t>fosu</t>
+  </si>
+  <si>
     <t>scrypt:32768:8:1$7KJKlyvP3YurWh0Q$abfb5fe4309042bac68638982b71fe59731793ae18ea9c28dfee0fdde2aa72433db98fde9ad04ae15647b72baa7f22a2d35017fabc2b6d5ca947653047565239</t>
   </si>
   <si>
+    <t>scrypt:32768:8:1$saqOGqWkD9F5xn3u$a94f67c970e9adfdde919a65ab2c3c94cd07cbac6a3fe50910bcc1bd439101061e5ea55d58f4f7d27b45b1bf484a1a3dee3b3a443a8d2f9f2e955f85d1657226</t>
+  </si>
+  <si>
     <t>estate</t>
   </si>
   <si>
+    <t>store</t>
+  </si>
+  <si>
     <t>2026-06-07 02:31:55</t>
+  </si>
+  <si>
+    <t>2026-06-11 04:44:44</t>
   </si>
 </sst>
 </file>
@@ -395,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -417,13 +429,27 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
